--- a/Data/EC/NIT-9003801478.xlsx
+++ b/Data/EC/NIT-9003801478.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08FAD78F-97BB-48D3-84C9-402591331891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA9BD330-876F-4F76-9CA8-24286FFFDEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C7071E9D-D096-450D-9FB5-093702181A3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0FA544AC-B2CF-49C0-AECF-18C0EFB7AA75}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="83">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -65,6 +65,78 @@
     <t>CC</t>
   </si>
   <si>
+    <t>73102359</t>
+  </si>
+  <si>
+    <t>JOSE LUIS SANTIAGO BANDA HERNANDEZ</t>
+  </si>
+  <si>
+    <t>2311</t>
+  </si>
+  <si>
+    <t>2310</t>
+  </si>
+  <si>
+    <t>9154177</t>
+  </si>
+  <si>
+    <t>EDUIN CARREAZO MALDONADO</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1149188769</t>
+  </si>
+  <si>
+    <t>CARLOS JULIO BABILONIA MARTINEZ</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
+    <t>1710</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>1708</t>
+  </si>
+  <si>
+    <t>1707</t>
+  </si>
+  <si>
+    <t>1706</t>
+  </si>
+  <si>
+    <t>1143358895</t>
+  </si>
+  <si>
+    <t>VANESSA ISABEL HERRERA NUÑEZ</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1047409673</t>
+  </si>
+  <si>
+    <t>JOSE LUIS VEGA BARRETO</t>
+  </si>
+  <si>
     <t>1050970734</t>
   </si>
   <si>
@@ -74,6 +146,12 @@
     <t>1608</t>
   </si>
   <si>
+    <t>1063151477</t>
+  </si>
+  <si>
+    <t>DOMYS MANUEL BALLESTERO BALLESTERO</t>
+  </si>
+  <si>
     <t>1143399917</t>
   </si>
   <si>
@@ -83,40 +161,13 @@
     <t>1702</t>
   </si>
   <si>
-    <t>1149188769</t>
-  </si>
-  <si>
-    <t>CARLOS JULIO BABILONIA MARTINEZ</t>
-  </si>
-  <si>
-    <t>1706</t>
-  </si>
-  <si>
-    <t>1707</t>
-  </si>
-  <si>
-    <t>1708</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>1803</t>
+    <t>1002200499</t>
+  </si>
+  <si>
+    <t>MARIA BERNARDA NUÑEZ CASTILLA</t>
+  </si>
+  <si>
+    <t>2508</t>
   </si>
   <si>
     <t>110144</t>
@@ -125,24 +176,15 @@
     <t>JHON JAIRO FLORES FERIA</t>
   </si>
   <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
     <t>1808</t>
   </si>
   <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1143358895</t>
-  </si>
-  <si>
-    <t>VANESSA ISABEL HERRERA NUÑEZ</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
     <t>20175389</t>
   </si>
   <si>
@@ -155,33 +197,12 @@
     <t>RAFAEL ANTONIO DAVILA MARTINEZ</t>
   </si>
   <si>
+    <t>1904</t>
+  </si>
+  <si>
     <t>1903</t>
   </si>
   <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>9154177</t>
-  </si>
-  <si>
-    <t>EDUIN CARREAZO MALDONADO</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1047409673</t>
-  </si>
-  <si>
-    <t>JOSE LUIS VEGA BARRETO</t>
-  </si>
-  <si>
-    <t>1063151477</t>
-  </si>
-  <si>
-    <t>DOMYS MANUEL BALLESTERO BALLESTERO</t>
-  </si>
-  <si>
     <t>1002189465</t>
   </si>
   <si>
@@ -194,21 +215,21 @@
     <t>JEAN CARLOS OLIVO MENDOZA</t>
   </si>
   <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
     <t>1909</t>
   </si>
   <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
     <t>1047495828</t>
   </si>
   <si>
@@ -224,22 +245,13 @@
     <t>YEISON GUILLERMO MIRANDA MACEA</t>
   </si>
   <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
     <t>2110</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>1002200499</t>
-  </si>
-  <si>
-    <t>MARIA BERNARDA NUÑEZ CASTILLA</t>
-  </si>
-  <si>
-    <t>2508</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -338,9 +350,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -353,7 +363,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -553,23 +565,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -597,10 +609,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -638,22 +650,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>667900</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>430650</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6CE9EA2-D11D-77A6-5109-41307B14CC15}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC8D4AAB-9103-03A8-84E9-F8B1FBE6B95D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -675,7 +687,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="921900" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1004,27 +1016,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAAD6550-97D9-4F8E-893E-C24B62AEB67F}">
-  <dimension ref="B2:J54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D04BA38-CF50-4033-8530-089E5057BB3C}">
+  <dimension ref="B2:J56"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1033,7 +1045,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1044,7 +1056,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1055,7 +1067,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1066,10 +1078,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1082,8 +1094,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1098,15 +1110,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>962106</v>
+        <v>1115766</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1114,27 +1126,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C13" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F13" s="5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1154,16 +1166,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1177,70 +1189,70 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>4596</v>
+        <v>76830</v>
       </c>
       <c r="G16" s="18">
-        <v>689454</v>
+        <v>1525335</v>
       </c>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>14</v>
-      </c>
       <c r="F17" s="18">
-        <v>27578</v>
+        <v>76830</v>
       </c>
       <c r="G17" s="18">
-        <v>689454</v>
+        <v>1525335</v>
       </c>
       <c r="H17" s="19"/>
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>17</v>
-      </c>
       <c r="F18" s="18">
-        <v>29509</v>
+        <v>33125</v>
       </c>
       <c r="G18" s="18">
-        <v>952333</v>
+        <v>828116</v>
       </c>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E19" s="16" t="s">
         <v>18</v>
@@ -1255,15 +1267,15 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>19</v>
@@ -1278,15 +1290,15 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" s="16" t="s">
         <v>20</v>
@@ -1301,15 +1313,15 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>21</v>
@@ -1324,15 +1336,15 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E23" s="16" t="s">
         <v>22</v>
@@ -1347,15 +1359,15 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24" s="16" t="s">
         <v>23</v>
@@ -1370,15 +1382,15 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E25" s="16" t="s">
         <v>24</v>
@@ -1393,15 +1405,15 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" s="16" t="s">
         <v>25</v>
@@ -1416,15 +1428,15 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>26</v>
@@ -1439,191 +1451,191 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>29</v>
-      </c>
       <c r="F28" s="18">
-        <v>31249</v>
+        <v>29509</v>
       </c>
       <c r="G28" s="18">
-        <v>781242</v>
+        <v>952333</v>
       </c>
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E29" s="16" t="s">
         <v>30</v>
       </c>
       <c r="F29" s="18">
-        <v>31249</v>
+        <v>34800</v>
       </c>
       <c r="G29" s="18">
-        <v>781242</v>
+        <v>870000</v>
       </c>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F30" s="18">
-        <v>12500</v>
+        <v>51304</v>
       </c>
       <c r="G30" s="18">
-        <v>781242</v>
+        <v>1282600</v>
       </c>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F31" s="18">
-        <v>34800</v>
+        <v>4596</v>
       </c>
       <c r="G31" s="18">
-        <v>870000</v>
+        <v>689454</v>
       </c>
       <c r="H31" s="19"/>
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F32" s="18">
-        <v>15625</v>
+        <v>33125</v>
       </c>
       <c r="G32" s="18">
-        <v>781242</v>
+        <v>828116</v>
       </c>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F33" s="18">
-        <v>27604</v>
+        <v>27578</v>
       </c>
       <c r="G33" s="18">
-        <v>908526</v>
+        <v>689454</v>
       </c>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F34" s="18">
-        <v>33125</v>
+        <v>26572</v>
       </c>
       <c r="G34" s="18">
-        <v>908526</v>
+        <v>1423500</v>
       </c>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F35" s="18">
-        <v>33125</v>
+        <v>12500</v>
       </c>
       <c r="G35" s="18">
-        <v>828116</v>
+        <v>781242</v>
       </c>
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1634,122 +1646,122 @@
         <v>45</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F36" s="18">
-        <v>51304</v>
+        <v>31249</v>
       </c>
       <c r="G36" s="18">
-        <v>1282600</v>
+        <v>781242</v>
       </c>
       <c r="H36" s="19"/>
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F37" s="18">
-        <v>33125</v>
+        <v>31249</v>
       </c>
       <c r="G37" s="18">
-        <v>828116</v>
+        <v>781242</v>
       </c>
       <c r="H37" s="19"/>
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F38" s="18">
-        <v>33125</v>
+        <v>15625</v>
       </c>
       <c r="G38" s="18">
-        <v>828116</v>
+        <v>781242</v>
       </c>
       <c r="H38" s="19"/>
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F39" s="18">
-        <v>19875</v>
+        <v>33125</v>
       </c>
       <c r="G39" s="18">
-        <v>828116</v>
+        <v>908526</v>
       </c>
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F40" s="18">
-        <v>33125</v>
+        <v>27604</v>
       </c>
       <c r="G40" s="18">
-        <v>828116</v>
+        <v>908526</v>
       </c>
       <c r="H40" s="19"/>
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F41" s="18">
         <v>33125</v>
@@ -1761,18 +1773,18 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F42" s="18">
         <v>33125</v>
@@ -1784,18 +1796,18 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F43" s="18">
         <v>33125</v>
@@ -1807,7 +1819,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1818,138 +1830,184 @@
         <v>58</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F44" s="18">
-        <v>24578</v>
+        <v>33125</v>
       </c>
       <c r="G44" s="18">
-        <v>877803</v>
+        <v>828116</v>
       </c>
       <c r="H44" s="19"/>
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E45" s="16" t="s">
         <v>62</v>
       </c>
       <c r="F45" s="18">
-        <v>21804</v>
+        <v>33125</v>
       </c>
       <c r="G45" s="18">
-        <v>908526</v>
+        <v>828116</v>
       </c>
       <c r="H45" s="19"/>
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E46" s="16" t="s">
         <v>63</v>
       </c>
       <c r="F46" s="18">
-        <v>36341</v>
+        <v>19875</v>
       </c>
       <c r="G46" s="18">
-        <v>908526</v>
+        <v>828116</v>
       </c>
       <c r="H46" s="19"/>
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F47" s="18">
-        <v>36341</v>
+        <v>24578</v>
       </c>
       <c r="G47" s="18">
-        <v>908526</v>
+        <v>877803</v>
       </c>
       <c r="H47" s="19"/>
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B48" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="D48" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="E48" s="22" t="s">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F48" s="24">
-        <v>26572</v>
-      </c>
-      <c r="G48" s="24">
-        <v>1423500</v>
-      </c>
-      <c r="H48" s="25"/>
-      <c r="I48" s="25"/>
-      <c r="J48" s="26"/>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B53" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C53" s="32"/>
-      <c r="H53" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B54" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="C54" s="32"/>
-      <c r="H54" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
+      <c r="D48" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F48" s="18">
+        <v>36341</v>
+      </c>
+      <c r="G48" s="18">
+        <v>908526</v>
+      </c>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="20"/>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B49" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F49" s="18">
+        <v>36341</v>
+      </c>
+      <c r="G49" s="18">
+        <v>908526</v>
+      </c>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="20"/>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="F50" s="24">
+        <v>21804</v>
+      </c>
+      <c r="G50" s="24">
+        <v>908526</v>
+      </c>
+      <c r="H50" s="25"/>
+      <c r="I50" s="25"/>
+      <c r="J50" s="26"/>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B55" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55" s="32"/>
+      <c r="H55" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B56" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C56" s="32"/>
+      <c r="H56" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="H55:J55"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
